--- a/Projects/Pistons_Players_Roster_2025-2026.xlsx
+++ b/Projects/Pistons_Players_Roster_2025-2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thejjserg/Documents/GitHub/basketball-analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A2C67E8-D011-5548-8078-720C9F7920EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0C334EB-CBE0-8A43-A120-F696B5160120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="15120" yWindow="660" windowWidth="15120" windowHeight="17680" xr2:uid="{910F67DB-3496-FA43-88B5-441A976AD162}"/>
   </bookViews>
